--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -1,41 +1,69 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\karacsony.zsuzsanna\Desktop\átlátható ktg.vetés\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2885375E-C1DD-4CFF-9DC8-3768AABD766C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="II. Alaptábla" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+  <si>
+    <t>Év</t>
+  </si>
+  <si>
+    <t>Összes kiadás (eFt)</t>
+  </si>
+  <si>
+    <t>Személyi jellegű (eFt)</t>
+  </si>
+  <si>
+    <t>Munkaadói járulék (eFt)</t>
+  </si>
+  <si>
+    <t>Dologi kiadás (eFt)</t>
+  </si>
+  <si>
+    <t>Pénzbeni juttatás (eFt)</t>
+  </si>
+  <si>
+    <t>Egyéb kiadás (eFt)</t>
+  </si>
+  <si>
+    <t>Szolidaritási hozzájárulás (eFt)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +93,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,256 +432,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.875" customWidth="1"/>
+    <col min="2" max="4" width="22.875" customWidth="1"/>
+    <col min="5" max="5" width="20.875" customWidth="1"/>
+    <col min="6" max="6" width="22.875" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="28.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Év</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Összes kiadás (eFt)</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Személyi jellegű (eFt)</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Munkaadói járulék (eFt)</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Dologi kiadás (eFt)</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Pénzbeni juttatás (eFt)</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Egyéb kiadás (eFt)</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Szolidaritási hozzájárulás (eFt)</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2019</v>
       </c>
       <c r="B2">
-        <v>3100000</v>
+        <f>C2+D2+E2+F2+G2+H2</f>
+        <v>852979</v>
       </c>
       <c r="C2">
-        <v>1050000</v>
+        <v>64370</v>
       </c>
       <c r="D2">
-        <v>210000</v>
+        <v>13322</v>
       </c>
       <c r="E2">
-        <v>980000</v>
+        <v>192163</v>
       </c>
       <c r="F2">
-        <v>320000</v>
+        <v>26536</v>
       </c>
       <c r="G2">
-        <v>290000</v>
+        <v>473114</v>
       </c>
       <c r="H2">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>83474</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2020</v>
       </c>
       <c r="B3">
-        <v>3000000</v>
+        <f t="shared" ref="B3:B9" si="0">C3+D3+E3+F3+G3+H3</f>
+        <v>1117312</v>
       </c>
       <c r="C3">
-        <v>1080000</v>
+        <v>75507</v>
       </c>
       <c r="D3">
-        <v>215000</v>
+        <v>14229</v>
       </c>
       <c r="E3">
-        <v>920000</v>
+        <v>212184</v>
       </c>
       <c r="F3">
-        <v>310000</v>
+        <v>38221</v>
       </c>
       <c r="G3">
-        <v>275000</v>
+        <v>720689</v>
       </c>
       <c r="H3">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>56482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
       <c r="B4">
-        <v>3350000</v>
+        <f t="shared" si="0"/>
+        <v>1319213</v>
       </c>
       <c r="C4">
-        <v>1120000</v>
+        <v>72600</v>
       </c>
       <c r="D4">
-        <v>225000</v>
+        <v>11600</v>
       </c>
       <c r="E4">
-        <v>1020000</v>
+        <v>155000</v>
       </c>
       <c r="F4">
-        <v>340000</v>
+        <v>22000</v>
       </c>
       <c r="G4">
-        <v>305000</v>
+        <v>866860</v>
       </c>
       <c r="H4">
-        <v>340000</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>191153</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2022</v>
       </c>
       <c r="B5">
-        <v>3700000</v>
+        <f t="shared" si="0"/>
+        <v>1852275</v>
       </c>
       <c r="C5">
-        <v>1200000</v>
+        <v>97848</v>
       </c>
       <c r="D5">
-        <v>240000</v>
+        <v>13200</v>
       </c>
       <c r="E5">
-        <v>1100000</v>
+        <v>271100</v>
       </c>
       <c r="F5">
-        <v>370000</v>
+        <v>22000</v>
       </c>
       <c r="G5">
-        <v>330000</v>
+        <v>1235006</v>
       </c>
       <c r="H5">
-        <v>460000</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>213121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2023</v>
       </c>
       <c r="B6">
-        <v>3950000</v>
+        <f t="shared" si="0"/>
+        <v>2312363</v>
       </c>
       <c r="C6">
-        <v>1280000</v>
+        <v>101860</v>
       </c>
       <c r="D6">
-        <v>255000</v>
+        <v>15280</v>
       </c>
       <c r="E6">
-        <v>1180000</v>
+        <v>369900</v>
       </c>
       <c r="F6">
-        <v>395000</v>
+        <v>27000</v>
       </c>
       <c r="G6">
-        <v>350000</v>
+        <v>1460033</v>
       </c>
       <c r="H6">
-        <v>490000</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>338290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2024</v>
       </c>
       <c r="B7">
-        <v>4200000</v>
+        <f t="shared" si="0"/>
+        <v>3006190</v>
       </c>
       <c r="C7">
-        <v>1350000</v>
+        <v>106120</v>
       </c>
       <c r="D7">
-        <v>270000</v>
+        <v>14600</v>
       </c>
       <c r="E7">
-        <v>1250000</v>
+        <v>408767</v>
       </c>
       <c r="F7">
-        <v>415000</v>
+        <v>31000</v>
       </c>
       <c r="G7">
-        <v>365000</v>
+        <v>2018456</v>
       </c>
       <c r="H7">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>427247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2025</v>
       </c>
       <c r="B8">
-        <v>4450000</v>
+        <f t="shared" si="0"/>
+        <v>1857890</v>
       </c>
       <c r="C8">
-        <v>1420000</v>
+        <v>138220</v>
       </c>
       <c r="D8">
-        <v>285000</v>
+        <v>19500</v>
       </c>
       <c r="E8">
-        <v>1320000</v>
+        <v>376800</v>
       </c>
       <c r="F8">
-        <v>440000</v>
+        <v>37000</v>
       </c>
       <c r="G8">
-        <v>380000</v>
+        <v>871828</v>
       </c>
       <c r="H8">
-        <v>605000</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>414542</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2026</v>
       </c>
       <c r="B9">
-        <v>4750000</v>
+        <f t="shared" si="0"/>
+        <v>2844024</v>
       </c>
       <c r="C9">
-        <v>1500000</v>
+        <v>173200</v>
       </c>
       <c r="D9">
-        <v>300000</v>
+        <v>22860</v>
       </c>
       <c r="E9">
-        <v>1400000</v>
+        <v>424100</v>
       </c>
       <c r="F9">
-        <v>465000</v>
+        <v>37000</v>
       </c>
       <c r="G9">
-        <v>395000</v>
+        <v>1703870</v>
       </c>
       <c r="H9">
-        <v>690000</v>
+        <v>482994</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="71" orientation="landscape" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H9"/>
+    <ignoredError sqref="A1:H1 A2:A9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/data/kiadas.xlsx
+++ b/public/data/kiadas.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2">
         <f>C2+D2+E2+F2+G2+H2</f>
-        <v>852979</v>
+        <v>641221</v>
       </c>
       <c r="C2">
         <v>64370</v>
@@ -491,7 +491,7 @@
         <v>26536</v>
       </c>
       <c r="G2">
-        <v>473114</v>
+        <v>261356</v>
       </c>
       <c r="H2">
         <v>83474</v>
@@ -503,7 +503,7 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B9" si="0">C3+D3+E3+F3+G3+H3</f>
-        <v>1117312</v>
+        <v>577226</v>
       </c>
       <c r="C3">
         <v>75507</v>
@@ -518,10 +518,10 @@
         <v>38221</v>
       </c>
       <c r="G3">
-        <v>720689</v>
+        <v>174611</v>
       </c>
       <c r="H3">
-        <v>56482</v>
+        <v>62474</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -530,7 +530,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>1319213</v>
+        <v>870597</v>
       </c>
       <c r="C4">
         <v>72600</v>
@@ -545,7 +545,7 @@
         <v>22000</v>
       </c>
       <c r="G4">
-        <v>866860</v>
+        <v>418244</v>
       </c>
       <c r="H4">
         <v>191153</v>
@@ -557,7 +557,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>1852275</v>
+        <v>1110781</v>
       </c>
       <c r="C5">
         <v>97848</v>
@@ -572,7 +572,7 @@
         <v>22000</v>
       </c>
       <c r="G5">
-        <v>1235006</v>
+        <v>493512</v>
       </c>
       <c r="H5">
         <v>213121</v>
@@ -584,7 +584,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>2312363</v>
+        <v>1438970</v>
       </c>
       <c r="C6">
         <v>101860</v>
@@ -599,7 +599,7 @@
         <v>27000</v>
       </c>
       <c r="G6">
-        <v>1460033</v>
+        <v>586640</v>
       </c>
       <c r="H6">
         <v>338290</v>
@@ -611,7 +611,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>3006190</v>
+        <v>1578898</v>
       </c>
       <c r="C7">
         <v>106120</v>
@@ -626,7 +626,7 @@
         <v>31000</v>
       </c>
       <c r="G7">
-        <v>2018456</v>
+        <v>591164</v>
       </c>
       <c r="H7">
         <v>427247</v>
@@ -638,7 +638,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>1857890</v>
+        <v>1557572</v>
       </c>
       <c r="C8">
         <v>138220</v>
@@ -653,10 +653,10 @@
         <v>37000</v>
       </c>
       <c r="G8">
-        <v>871828</v>
+        <v>408731</v>
       </c>
       <c r="H8">
-        <v>414542</v>
+        <v>577321</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -665,7 +665,7 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>2844024</v>
+        <v>1817108</v>
       </c>
       <c r="C9">
         <v>173200</v>
@@ -680,7 +680,7 @@
         <v>37000</v>
       </c>
       <c r="G9">
-        <v>1703870</v>
+        <v>676954</v>
       </c>
       <c r="H9">
         <v>482994</v>
